--- a/output/2026-09-13_12_Croazia_Bjelovarsko-bilogorska_Cleaning.xlsx
+++ b/output/2026-09-13_12_Croazia_Bjelovarsko-bilogorska_Cleaning.xlsx
@@ -481,7 +481,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rivenditore e centro assistenza ufficiale Kärcher, Nilfisk-Alto/Wap, Rotowash, Annavi, Roto (idropulitrici, aspiratori, lavasciuga pavimenti). Unico distributore specializzato in attrezzature per pulizia professionale/industriale rilevato nella provincia. Verificato su fininfo.hr, poslovna.hr e sito ufficiale.</t>
+          <t>Rivenditore e centro assistenza ufficiale Kärcher, Nilfisk-Alto/Wap, Rotowash, Annavi, Roto (idropulitrici, aspiratori, lavasciuga pavimenti). Unico distributore specializzato in attrezzature per pulizia professionale/industriale rilevato nella provincia. Verificato su fininfo.hr, poslovna.hr e sito ufficiale. [DUPLICATO — vedi anche: 2026-09-13_02_Croazia_Varazdinska_ATEX_Equipment-Services.xlsx]</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
